--- a/SS3 models/PRFL/06_Base_Final/bootstrap/01_tables.xlsx
+++ b/SS3 models/PRFL/06_Base_Final/bootstrap/01_tables.xlsx
@@ -6,15 +6,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="01_Quants" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_RefPoints" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Sensitivies" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_Quants" sheetId="7" state="visible" r:id="rId1"/>
+    <sheet name="02_RefPoints" sheetId="8" state="visible" r:id="rId2"/>
+    <sheet name="03_Sensitivies" sheetId="9" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -614,6 +614,42 @@
   </si>
   <si>
     <t xml:space="preserve">0.99 (0.98 - 0.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (0.005 - 0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025/Fmsy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.043 (0.024 - 0.077)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42 (2.25 - 4.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025/SSBmsst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49 (3.06 - 3.87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch_2023-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (0.04 - 0.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91 (0.88 - 0.95)</t>
   </si>
 </sst>
 </file>
@@ -2311,18 +2347,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5">
@@ -2335,18 +2371,18 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
@@ -2359,10 +2395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B9" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -2375,10 +2411,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
